--- a/data/trans_orig/IP28-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP28-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69888</t>
+          <t>69219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80726</t>
+          <t>80921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66841</t>
+          <t>66339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>77566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138997</t>
+          <t>139370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155408</t>
+          <t>155270</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>30189</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>48840</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>49050</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72521</t>
+          <t>71864</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>330814</t>
+          <t>329021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>354609</t>
+          <t>353875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>374772</t>
+          <t>374985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>400830</t>
+          <t>401536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>715728</t>
+          <t>713003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>749531</t>
+          <t>749482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32935</t>
+          <t>31602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51900</t>
+          <t>52860</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>30464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49241</t>
+          <t>49780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68479</t>
+          <t>66910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95171</t>
+          <t>94848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>21005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>19715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18573</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>35509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>138261</t>
+          <t>137329</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>152377</t>
+          <t>152800</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125309</t>
+          <t>124788</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>139425</t>
+          <t>139992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>268027</t>
+          <t>267866</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>289563</t>
+          <t>289329</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16895</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32674</t>
+          <t>33044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54564</t>
+          <t>53773</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44221</t>
+          <t>43674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67508</t>
+          <t>66066</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82942</t>
+          <t>84475</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114756</t>
+          <t>114133</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>549248</t>
+          <t>550624</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>580406</t>
+          <t>580529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>578036</t>
+          <t>577721</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>610067</t>
+          <t>610060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1137836</t>
+          <t>1136423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1181615</t>
+          <t>1181076</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43328</t>
+          <t>42521</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>64441</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68988</t>
+          <t>69309</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>95750</t>
+          <t>94968</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128261</t>
+          <t>126998</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24919</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9364</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56879</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68967</t>
+          <t>68664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54478</t>
+          <t>54261</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65272</t>
+          <t>65470</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113630</t>
+          <t>114564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131018</t>
+          <t>131879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>23558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33467</t>
+          <t>32304</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42112</t>
+          <t>42689</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>46459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69021</t>
+          <t>69801</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>308472</t>
+          <t>309658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>337268</t>
+          <t>336696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>346859</t>
+          <t>345941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>374743</t>
+          <t>373114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>667397</t>
+          <t>664693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>705063</t>
+          <t>704573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66209</t>
+          <t>64817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36653</t>
+          <t>37243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59360</t>
+          <t>59910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84259</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115683</t>
+          <t>118044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15598</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17378</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17394</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>34577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121730</t>
+          <t>121795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136799</t>
+          <t>136917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>132188</t>
+          <t>132056</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>147614</t>
+          <t>146820</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>259617</t>
+          <t>258846</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>281346</t>
+          <t>280458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26004</t>
+          <t>26257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53471</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41812</t>
+          <t>41757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64666</t>
+          <t>64170</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81848</t>
+          <t>82873</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112657</t>
+          <t>113505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>500896</t>
+          <t>501246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>534753</t>
+          <t>533769</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,82 +5075,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>82,58%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>563367</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>545831</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>579122</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>81,8%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>79,26%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>84,09%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1080717</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1057375</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1104491</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>80,95%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>79,2%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>82,73%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>803</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>563367</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>542876</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>577697</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>81,8%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>83,88%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1551</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1080717</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1056436</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1103995</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>80,95%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>79,13%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>59607</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87172</t>
+          <t>87324</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>49365</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75300</t>
+          <t>74947</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>115495</t>
+          <t>115906</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>153083</t>
+          <t>152249</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17182</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33541</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45611</t>
+          <t>45820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48404</t>
+          <t>48455</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>56812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88385</t>
+          <t>88703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100322</t>
+          <t>100818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>15032</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20340</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>36898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31244</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50520</t>
+          <t>50750</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>368719</t>
+          <t>368781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>389646</t>
+          <t>389378</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>361232</t>
+          <t>362541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>386792</t>
+          <t>386552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>738039</t>
+          <t>738351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>770656</t>
+          <t>771952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>22124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40668</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47049</t>
+          <t>47798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72912</t>
+          <t>73141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27845</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126940</t>
+          <t>126065</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>140750</t>
+          <t>140475</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>139015</t>
+          <t>139290</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>153338</t>
+          <t>153228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>269334</t>
+          <t>269633</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>290502</t>
+          <t>290607</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20146</t>
+          <t>19580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>31843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50537</t>
+          <t>50011</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>50880</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>77021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>543558</t>
+          <t>543039</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>568704</t>
+          <t>568829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>559076</t>
+          <t>558800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>588912</t>
+          <t>589545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1110906</t>
+          <t>1109985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1149891</t>
+          <t>1150956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>36429</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>57137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58248</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>77666</t>
+          <t>79374</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>108343</t>
+          <t>110206</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>18689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42783</t>
+          <t>42710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53839</t>
+          <t>54030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83338</t>
+          <t>83147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102038</t>
+          <t>101630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>721</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43501</t>
+          <t>43715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34383</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67001</t>
+          <t>66352</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64741</t>
+          <t>64161</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>100711</t>
+          <t>101456</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>372682</t>
+          <t>372548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>402930</t>
+          <t>403332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>390054</t>
+          <t>393843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>432978</t>
+          <t>433672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>775514</t>
+          <t>775050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>827383</t>
+          <t>826761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20130</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39900</t>
+          <t>39931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33622</t>
+          <t>33785</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63023</t>
+          <t>62883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60923</t>
+          <t>59024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>93755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24454</t>
+          <t>24788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25983</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46048</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>111981</t>
+          <t>110516</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>127553</t>
+          <t>127441</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>148239</t>
+          <t>148735</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>165133</t>
+          <t>164900</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>264822</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>288034</t>
+          <t>288319</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>23906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>45356</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72933</t>
+          <t>72148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54652</t>
+          <t>54868</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90386</t>
+          <t>90894</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108679</t>
+          <t>107450</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153007</t>
+          <t>155325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>533041</t>
+          <t>534273</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>571121</t>
+          <t>570819</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>601400</t>
+          <t>597744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>646419</t>
+          <t>645724</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1143555</t>
+          <t>1143706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1203450</t>
+          <t>1203964</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,8%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30678</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53146</t>
+          <t>54722</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>44650</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74933</t>
+          <t>75901</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,47 +10237,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>99796</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>81887</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>120687</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>5,77%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>99796</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>81884</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>119950</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25321</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
